--- a/Assessment Questions/CDA/DBM-120/SQL Basics/Introduction to Databases, SQL, SQL Commands/SQL_Scenario_Advanced.xlsx
+++ b/Assessment Questions/CDA/DBM-120/SQL Basics/Introduction to Databases, SQL, SQL Commands/SQL_Scenario_Advanced.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Scenario Based" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,613 +413,456 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>DATABASE SCHEMA</t>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Option D</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Employees(emp_id, emp_name, age, salary, dept_id, joining_date)</t>
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SQL_Scenario_Advanced</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>A company stores employee records in a database. Which SQL command should be used to retrieve all records from the Employees table?</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Departments(dept_id, dept_name)</t>
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SQL_Scenario_Advanced</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A manager wants to filter employees based on total salary after grouping them by department. Which SQL clause should be used for filtering aggregated results?</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Assume tables are pre-populated with realistic company data.</t>
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SQL_Scenario_Advanced</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>You need to remove all records from a table but keep its structure intact for future use. Which SQL command is most appropriate?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SQL_Scenario_Advanced</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A developer wants to modify existing employee salary values in the database. Which SQL command should be used?</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SAMPLE DATA (for reference)</t>
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SQL_Scenario_Advanced</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A report needs to display employee salaries in descending order. Which SQL clause helps achieve this?</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>emp_id</t>
-        </is>
+      <c r="A7" t="n">
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>emp_name</t>
+          <t>SQL_Scenario_Advanced</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>salary</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>dept_id</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>joining_date</t>
+          <t>A data analyst wants to calculate the average salary of employees. Which SQL function should be used?</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amit</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>25</v>
-      </c>
-      <c r="D8" t="n">
-        <v>40000</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2022-01-10</t>
+          <t>SQL_Scenario_Advanced</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>You are asked to display complete employee details for reporting purposes. Write a query to retrieve all records from the Employees table.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Neha</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>30</v>
-      </c>
-      <c r="D9" t="n">
-        <v>60000</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2021-03-15</t>
+          <t>SQL_Scenario_Advanced</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HR wants a report showing only employee names and their salaries. Write a query to display only emp_name and salary.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Raj</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>28</v>
-      </c>
-      <c r="D10" t="n">
-        <v>55000</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2020-07-20</t>
+          <t>SQL_Scenario_Advanced</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A manager wants to identify employees earning more than 50000. Write a query to filter such employees.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Simran</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>35</v>
-      </c>
-      <c r="D11" t="n">
-        <v>70000</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2019-11-01</t>
+          <t>SQL_Scenario_Advanced</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>The IT department wants a list of employees belonging to dept_id = 1. Write a query to retrieve them.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kiran</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>26</v>
-      </c>
-      <c r="D12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="E12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2023-06-12</t>
+          <t>SQL_Scenario_Advanced</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>The finance team wants employees sorted by highest salary first. Write a query to sort employees by salary in descending order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SQL_Scenario_Advanced</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A report requires identifying employees older than 30 years. Write a query to filter employees based on age.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Q.No</t>
-        </is>
+      <c r="A14" t="n">
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>SQL_Scenario_Advanced</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Scenario Question</t>
+          <t>Management wants to know how many unique departments exist in the Employees table. Write a query to display distinct dept_id values.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>SQL_Scenario_Advanced</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>A company stores employee records in a database. Which SQL command should be used to retrieve all records from the Employees table?</t>
+          <t>A search feature needs to find employees whose names start with the letter 'A'. Write a query for this requirement.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>SQL_Scenario_Advanced</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>A manager wants to filter employees based on total salary after grouping them by department. Which SQL clause should be used for filtering aggregated results?</t>
+          <t>HR needs to know the total number of employees in the company. Write a query to count employees.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>SQL_Scenario_Advanced</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>You need to remove all records from a table but keep its structure intact for future use. Which SQL command is most appropriate?</t>
+          <t>Finance team wants to calculate the average salary of employees. Write a query to compute it.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>SQL_Scenario_Advanced</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>A developer wants to modify existing employee salary values in the database. Which SQL command should be used?</t>
+          <t>Management wants to identify the highest salary in the organization. Write a query to find it.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>SQL_Scenario_Advanced</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A report needs to display employee salaries in descending order. Which SQL clause helps achieve this?</t>
+          <t>HR needs a list of employees earning between 40000 and 60000. Write a query to filter them.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>SQL_Scenario_Advanced</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A data analyst wants to calculate the average salary of employees. Which SQL function should be used?</t>
+          <t>A report needs employees sorted based on their joining date. Write a query to order results by joining_date.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Practical</t>
+          <t>SQL_Scenario_Advanced</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
-        <is>
-          <t>You are asked to display complete employee details for reporting purposes. Write a query to retrieve all records from the Employees table.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>8</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Practical</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>HR wants a report showing only employee names and their salaries. Write a query to display only emp_name and salary.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>9</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Practical</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>A manager wants to identify employees earning more than 50000. Write a query to filter such employees.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>10</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Practical</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>The IT department wants a list of employees belonging to dept_id = 1. Write a query to retrieve them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>11</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Practical</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>The finance team wants employees sorted by highest salary first. Write a query to sort employees by salary in descending order.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>12</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Practical</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>A report requires identifying employees older than 30 years. Write a query to filter employees based on age.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>13</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Practical</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Management wants to know how many unique departments exist in the Employees table. Write a query to display distinct dept_id values.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>14</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Practical</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>A search feature needs to find employees whose names start with the letter 'A'. Write a query for this requirement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>15</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Practical</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>HR needs to know the total number of employees in the company. Write a query to count employees.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>16</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Practical</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Finance team wants to calculate the average salary of employees. Write a query to compute it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>17</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Practical</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Management wants to identify the highest salary in the organization. Write a query to find it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>18</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Practical</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>HR needs a list of employees earning between 40000 and 60000. Write a query to filter them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>19</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Practical</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>A report needs employees sorted based on their joining date. Write a query to order results by joining_date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>20</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Practical</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
         <is>
           <t>The CEO wants to identify the top 3 highest-paid employees in the company. Write a query to retrieve these employees.</t>
         </is>
